--- a/Vulnerability_Test_Report.xlsx
+++ b/Vulnerability_Test_Report.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1216,17 +1216,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Info Disclosure detected.</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: XSS (Reflected) detected.</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: XSS (Reflected) detected.</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Warning: Missing Headers detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Warning: XSS (Reflected) detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>Warning: Path Traversal detected.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2162,17 +2162,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: IDOR detected.</t>
         </is>
       </c>
     </row>
@@ -2184,17 +2184,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Warning: XSS (Reflected) detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Path Traversal detected.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -2514,17 +2514,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2800,17 +2800,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Warning: Path Traversal detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: SQL Injection detected.</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Path Traversal detected.</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Missing Headers detected.</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Info Disclosure detected.</t>
         </is>
       </c>
     </row>
@@ -4648,17 +4648,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Warning: SQL Injection detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Info Disclosure detected.</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4736,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: IDOR detected.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5550,17 +5550,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: SQL Injection detected.</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Warning: IDOR detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Path Traversal detected.</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6276,17 +6276,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: Info Disclosure detected.</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for IDOR</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: IDOR detected.</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6628,17 +6628,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>No vulnerabilities detected on endpoint.</t>
+          <t>Warning: SQL Injection detected.</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6738,17 +6738,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Warning: Info Disclosure detected.</t>
+          <t>No vulnerabilities detected on endpoint.</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
+          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for SQL Injection</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for Info Disclosure</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Missing Headers</t>
+          <t>OWASP ZAP Baseline Scan for IDOR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OWASP ZAP Baseline Scan for Path Traversal</t>
+          <t>OWASP ZAP Baseline Scan for XSS (Reflected)</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
